--- a/artfynd/A 22231-2022 artfynd.xlsx
+++ b/artfynd/A 22231-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22231-2022 artfynd.xlsx
+++ b/artfynd/A 22231-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91847713</v>
+        <v>91847715</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428314.1731928394</v>
+        <v>428296</v>
       </c>
       <c r="R2" t="n">
-        <v>7004999.200861082</v>
+        <v>7005124</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,53 +776,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91847715</v>
+        <v>94509444</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Håckrenmagasinet, Fjällviken /S/, grusväg, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428296.1210273502</v>
+        <v>428480</v>
       </c>
       <c r="R3" t="n">
-        <v>7005123.881322555</v>
+        <v>7005188</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Den södra kanten av grusväg söder om Fjällviken. 5 plantor i en grupp i vägens innerslänt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,72 +877,80 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant grusväg, innerslänt</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>Atlasinventering och läger i Jämtland</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91847714</v>
+        <v>94509745</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Rörtjärnbäcken, O sida 120 m S om grusväg, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428146.8034072338</v>
+        <v>428618</v>
       </c>
       <c r="R4" t="n">
-        <v>7004860.101196455</v>
+        <v>7005101</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Längs 15 m strand av Rörtjärnbäcken, på den O sidan 120 m S om bro för grusväg. Flack strand med stenigt underlag i öppen granskog. Korallrot även ute i grunt vatten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,25 +993,133 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Strand av bäck</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Atlasinventering och läger i Jämtland</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111018601</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rörtjärnsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>428630</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7005078</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mörsil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
